--- a/data/trending_integrated_20260917_12.xlsx
+++ b/data/trending_integrated_20260917_12.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>1705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.43%</t>
+          <t>'+22.05%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="H2" t="n">
-        <v>3.71</v>
+        <v>3.52</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>56</v>
+        <v>1397</v>
       </c>
       <c r="K2" t="n">
-        <v>56</v>
+        <v>1395</v>
       </c>
       <c r="L2" t="n">
-        <v>90</v>
+        <v>1800</v>
       </c>
       <c r="M2" t="n">
-        <v>56</v>
+        <v>1369</v>
       </c>
       <c r="N2" t="n">
-        <v>3.71</v>
+        <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>432471722</v>
+        <v>43855532317</v>
       </c>
       <c r="P2" t="n">
-        <v>901</v>
+        <v>5140</v>
       </c>
       <c r="Q2" t="n">
-        <v>56</v>
+        <v>870</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>마이크로LED 및 AI 데이터센터 관련 신규 사업 기대감. BPS 대비 주가 저평가 및 상승 가능성 언급.</t>
+          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['마이크로LED', 'AI데이터센터', 'BPS']</t>
+          <t>['우주', '스페이스X', '유상증자']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>321370</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1687</v>
+        <v>68</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.76%</t>
+          <t>'+21.43%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="H3" t="n">
-        <v>3.52</v>
+        <v>3.71</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1397</v>
+        <v>56</v>
       </c>
       <c r="K3" t="n">
-        <v>1395</v>
+        <v>56</v>
       </c>
       <c r="L3" t="n">
-        <v>1800</v>
+        <v>90</v>
       </c>
       <c r="M3" t="n">
-        <v>1369</v>
+        <v>56</v>
       </c>
       <c r="N3" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="O3" t="n">
-        <v>41937716144</v>
+        <v>432471722</v>
       </c>
       <c r="P3" t="n">
-        <v>5140</v>
+        <v>901</v>
       </c>
       <c r="Q3" t="n">
-        <v>870</v>
+        <v>56</v>
       </c>
       <c r="R3" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
+          <t>마이크로LED, AI 데이터센터 관련 잠재력 언급. 그러나 거래량 부진 및 개미 투자자 심리 불안정.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['우주', '스페이스X', '유상증자']</t>
+          <t>['마이크로LED', 'AI', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>321370</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4610</v>
+        <v>4575</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.05%</t>
+          <t>'+19.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="F4" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G4" t="n">
-        <v>1051</v>
+        <v>1079</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>214988526250</v>
+        <v>219333078546</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오 및 소프트뱅크 인수설 기반의 텐버거 기대감. 대량 거래 동반한 주가 급등 가능성 언급.</t>
+          <t>소프트뱅크의 인수설 및 카카오와의 협력 기대감으로 급등. 텐버거 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
+          <t>['인수설', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -860,7 +860,7 @@
         <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>255968976870</v>
+        <v>257960166895</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3935</v>
+        <v>3870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.43%</t>
+          <t>'+10.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>81220553139</v>
+        <v>84506071430</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 관련 이슈 및 프로그램 매수세 유입에 따른 주가 상승 전망. 일부에서는 우주 섹터와 무관하다는 부정적 의견도 존재.</t>
+          <t>스페이스X 관련 이슈로 인한 변동성 장세. 프로그램 매수와 매도세가 공존하며 방향성 부재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '프로그램매수', '우주섹터']</t>
+          <t>['스페이스X', '프로그램매매', '변동성']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21500</v>
+        <v>21600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.44%</t>
+          <t>'+6.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>54947043125</v>
+        <v>56254292300</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 기관 매수세 유입에 따른 주가 상승 기대감. 60일선 돌파 및 추세 전환 가능성 언급.</t>
+          <t>나스닥 반등과 금리 인상에도 불구하고 긍정적 전망. 투자의견 '매수' 및 목표주가 4만원 유지.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['나스닥', '기관매수', '추세전환']</t>
+          <t>['금리 인상', '투자의견', '목표주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10440</v>
+        <v>10480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.71%</t>
+          <t>'+5.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>168634903975</v>
+        <v>169186761335</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13390</v>
+        <v>13370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.64%</t>
+          <t>'+3.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>49011695965</v>
+        <v>49497951760</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1314,13 +1314,13 @@
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F10" t="n">
         <v>107</v>
       </c>
       <c r="G10" t="n">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>83963354550</v>
+        <v>85233960000</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1391,162 +1391,162 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18600</v>
+        <v>16170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="G11" t="n">
-        <v>290</v>
+        <v>1194</v>
       </c>
       <c r="H11" t="n">
-        <v>10.85</v>
+        <v>4.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18570</v>
+        <v>16100</v>
       </c>
       <c r="K11" t="n">
-        <v>18740</v>
+        <v>16200</v>
       </c>
       <c r="L11" t="n">
-        <v>18900</v>
+        <v>16750</v>
       </c>
       <c r="M11" t="n">
-        <v>18510</v>
+        <v>15560</v>
       </c>
       <c r="N11" t="n">
-        <v>10.64</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>40814952000</v>
+        <v>313262334035</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-175000</v>
+        <v>-508000</v>
       </c>
       <c r="S11" t="n">
-        <v>-31000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6천억 수주 발표 및 대차해지 운동 언급. 정부의 웨스팅하우스 지분 인수 타진 소식.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주', '대차해지', '웨스팅하우스']</t>
+          <t>['광통신', '미국', '수혜']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16120</v>
+        <v>18550</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'-0.11%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>1164</v>
+        <v>295</v>
       </c>
       <c r="H12" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K12" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L12" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M12" t="n">
-        <v>15560</v>
+        <v>18510</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>310473485590</v>
+        <v>41980600660</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-508000</v>
+        <v>-175000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
+          <t>6천억 수주에도 불구하고 음봉 마감. 금리 인상 및 대차해지 운동으로 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '수혜']</t>
+          <t>['수주', '금리 인상', '대차해지']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
         <v>437</v>
       </c>
       <c r="G13" t="n">
-        <v>1828</v>
+        <v>1807</v>
       </c>
       <c r="H13" t="n">
         <v>46.52</v>
@@ -1622,7 +1622,7 @@
         <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>1287071330000</v>
+        <v>1320873877750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>게시글 대부분이 정치적 논쟁으로 이루어져 주가 관련 분석 부재. 반도체 시장 독점 및 국힘 정권 3년 허송세월 언급.</t>
+          <t>정치적 논쟁으로 인해 투자 심리가 혼조세를 보임. 주가 변동이 크지 않아 투자 동력 부재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1682,13 +1682,13 @@
         <v>-0.12</v>
       </c>
       <c r="E14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="H14" t="n">
         <v>26.54</v>
@@ -1714,7 +1714,7 @@
         <v>26.66</v>
       </c>
       <c r="O14" t="n">
-        <v>9149142450</v>
+        <v>9246497725</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1745000</v>
+        <v>1743000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.80%</t>
+          <t>'-0.91%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G15" t="n">
-        <v>1465</v>
+        <v>1451</v>
       </c>
       <c r="H15" t="n">
         <v>50.2</v>
@@ -1806,7 +1806,7 @@
         <v>50.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2339678295500</v>
+        <v>2391041164000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대만 증시 상승 및 악재 소멸에 따른 주가 상승 기대감. 미국 금리 인상 가능성 언급.</t>
+          <t>9월 악재 소멸 후 상승 기대감. JP모간의 매수세 유입 감지.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대만증시', '악재소멸', '금리인상']</t>
+          <t>['악재 소멸', '상승', '매수세']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13730</v>
+        <v>13790</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.29%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F16" t="n">
         <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>13026528125</v>
+        <v>13155731000</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1958,13 +1958,13 @@
         <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H17" t="n">
         <v>2.26</v>
@@ -1984,13 +1984,13 @@
         <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>3435</v>
+        <v>3420</v>
       </c>
       <c r="N17" t="n">
         <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>5128869213</v>
+        <v>5208273243</v>
       </c>
       <c r="P17" t="n">
         <v>16110</v>
@@ -2035,70 +2035,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13200</v>
+        <v>10170</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.36</v>
+        <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>18.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13530</v>
+        <v>10460</v>
       </c>
       <c r="K18" t="n">
-        <v>14280</v>
+        <v>10860</v>
       </c>
       <c r="L18" t="n">
-        <v>14800</v>
+        <v>11150</v>
       </c>
       <c r="M18" t="n">
-        <v>12960</v>
+        <v>10060</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>78798008055</v>
+        <v>54338950265</v>
       </c>
       <c r="P18" t="n">
-        <v>25700</v>
+        <v>22450</v>
       </c>
       <c r="Q18" t="n">
-        <v>4600</v>
+        <v>1760</v>
       </c>
       <c r="R18" t="n">
-        <v>-64000</v>
+        <v>-60000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10200</v>
+        <v>13110</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.49%</t>
+          <t>'-3.10%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.8</v>
+        <v>1.36</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F19" t="n">
         <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="H19" t="n">
-        <v>18.42</v>
+        <v>1.76</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10460</v>
+        <v>13530</v>
       </c>
       <c r="K19" t="n">
-        <v>10860</v>
+        <v>14280</v>
       </c>
       <c r="L19" t="n">
-        <v>11150</v>
+        <v>14800</v>
       </c>
       <c r="M19" t="n">
-        <v>10060</v>
+        <v>12960</v>
       </c>
       <c r="N19" t="n">
-        <v>19.22</v>
+        <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>54163458670</v>
+        <v>79018378185</v>
       </c>
       <c r="P19" t="n">
-        <v>22450</v>
+        <v>25700</v>
       </c>
       <c r="Q19" t="n">
-        <v>1760</v>
+        <v>4600</v>
       </c>
       <c r="R19" t="n">
-        <v>-60000</v>
+        <v>-64000</v>
       </c>
       <c r="S19" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4125</v>
+        <v>4085</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.46%</t>
+          <t>'-7.37%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>43305772517</v>
+        <v>43984109072</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_12.xlsx
+++ b/data/trending_integrated_20260917_12.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.05%</t>
+          <t>'+22.19%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" t="n">
         <v>3.52</v>
@@ -610,7 +610,7 @@
         <v>3.57</v>
       </c>
       <c r="O2" t="n">
-        <v>43855532317</v>
+        <v>44823405132</v>
       </c>
       <c r="P2" t="n">
         <v>5140</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="H3" t="n">
         <v>3.71</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>마이크로LED, AI 데이터센터 관련 잠재력 언급. 그러나 거래량 부진 및 개미 투자자 심리 불안정.</t>
+          <t>마이크로LED, AI 데이터센터 관련 기대감 속에서 300원 이상 상승 희망. BPS 715원 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크로LED', 'AI', '거래량']</t>
+          <t>['마이크로LED', 'AI 데이터센터', 'BPS']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4575</v>
+        <v>4600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.14%</t>
+          <t>'+19.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="F4" t="n">
         <v>202</v>
       </c>
       <c r="G4" t="n">
-        <v>1079</v>
+        <v>1115</v>
       </c>
       <c r="H4" t="n">
         <v>0.95</v>
@@ -794,7 +794,7 @@
         <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>219333078546</v>
+        <v>222264989520</v>
       </c>
       <c r="P4" t="n">
         <v>6900</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>소프트뱅크의 인수설 및 카카오와의 협력 기대감으로 급등. 텐버거 기대감 형성.</t>
+          <t>카카오 또는 소프트뱅크의 인수 가능성 언급. 10배 상승 및 1만원 이상 시가총액 기대. 거래량 급증.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수설', '소프트뱅크', '텐버거']</t>
+          <t>['인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21650</v>
+        <v>21850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+16.65%</t>
+          <t>'+17.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>257960166895</v>
+        <v>262141144870</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자회사 ADST의 CPO 생산장비 수주 및 삼성과의 공급 계약 체결. 3분기 영업이익 대폭 상승.</t>
+          <t>자회사 ADS테크의 CPO 생산 장비 수주 및 삼성 공급 계약 발표. AI 인프라 사업 확장 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['CPO', '수주', '공급계약']</t>
+          <t>['CPO', '수주', 'AI 인프라']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3870</v>
+        <v>3845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.57%</t>
+          <t>'+9.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F6" t="n">
         <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>84506071430</v>
+        <v>85556855718</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>56254292300</v>
+        <v>57278867775</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등과 금리 인상에도 불구하고 긍정적 전망. 투자의견 '매수' 및 목표주가 4만원 유지.</t>
+          <t>나스닥 반등 및 금리 인상 영향 속에서 장기 보유 및 분할 매수 관점 제시. 스퀴즈온 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['금리 인상', '투자의견', '목표주가']</t>
+          <t>['나스닥', '금리인상', '스퀴즈온']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10480</v>
+        <v>10460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.12%</t>
+          <t>'+4.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F8" t="n">
         <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>169186761335</v>
+        <v>169601165085</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 기대감으로 인한 주가 상승 전망. 그러나 주가 급등 후 차익실현 매물 출회 가능성 언급.</t>
+          <t>낙태약 및 탈모 치료 관련 기대감 속에서 외국인 매도세 관측. 1조원 이상 예상 매출 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '수혜주']</t>
+          <t>['낙태약', '탈모 치료', '매출 예상']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13370</v>
+        <v>13350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.48%</t>
+          <t>'+3.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>49497951760</v>
+        <v>49779661580</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85700</v>
+        <v>85600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>162</v>
       </c>
       <c r="F10" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" t="n">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>85233960000</v>
+        <v>86196855300</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16170</v>
+        <v>253250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>217</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>441</v>
       </c>
       <c r="G11" t="n">
-        <v>1194</v>
+        <v>1761</v>
       </c>
       <c r="H11" t="n">
-        <v>4.88</v>
+        <v>46.52</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16100</v>
+        <v>250500</v>
       </c>
       <c r="K11" t="n">
-        <v>16200</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16750</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>15560</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>313262334035</v>
+        <v>1349559000000</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-508000</v>
+        <v>-199000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-55000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
+          <t>정치적 논쟁이 주된 내용으로, 주가 및 실적 관련 구체적인 내용은 부재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '수혜']</t>
+          <t>['정치', '대선', '주식방']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18550</v>
+        <v>16150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'+0.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>2.93</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="G12" t="n">
-        <v>295</v>
+        <v>1213</v>
       </c>
       <c r="H12" t="n">
-        <v>10.85</v>
+        <v>4.88</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18570</v>
+        <v>16100</v>
       </c>
       <c r="K12" t="n">
-        <v>18740</v>
+        <v>16200</v>
       </c>
       <c r="L12" t="n">
-        <v>18900</v>
+        <v>16750</v>
       </c>
       <c r="M12" t="n">
-        <v>18510</v>
+        <v>15560</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>41980600660</v>
+        <v>315179767470</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-175000</v>
+        <v>-508000</v>
       </c>
       <c r="S12" t="n">
-        <v>-31000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6천억 수주에도 불구하고 음봉 마감. 금리 인상 및 대차해지 운동으로 투자 심리 위축.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '금리 인상', '대차해지']</t>
+          <t>['광통신', '미국', '수혜']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>253000</v>
+        <v>18590</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="F13" t="n">
-        <v>437</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>1807</v>
+        <v>305</v>
       </c>
       <c r="H13" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>253500</v>
+        <v>18570</v>
       </c>
       <c r="K13" t="n">
-        <v>257000</v>
+        <v>18740</v>
       </c>
       <c r="L13" t="n">
-        <v>259000</v>
+        <v>18900</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>18510</v>
       </c>
       <c r="N13" t="n">
-        <v>46.56</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1320873877750</v>
+        <v>42494992580</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-199000</v>
+        <v>-175000</v>
       </c>
       <c r="S13" t="n">
-        <v>-55000</v>
+        <v>-31000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 논쟁으로 인해 투자 심리가 혼조세를 보임. 주가 변동이 크지 않아 투자 동력 부재.</t>
+          <t>6천억 수주 발표에도 음봉 기록. 금리 인상 및 대차해지 운동 독려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['수주', '금리인상', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8410</v>
+        <v>8400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.71%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.12</v>
       </c>
       <c r="E14" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H14" t="n">
         <v>26.54</v>
@@ -1714,7 +1714,7 @@
         <v>26.66</v>
       </c>
       <c r="O14" t="n">
-        <v>9246497725</v>
+        <v>9408745110</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중국 디스플레이 산업에 밀린다는 부정적 전망. 높은 부채 비율 및 연이은 하락세로 인한 투자 심리 악화.</t>
+          <t>중국 경쟁 심화 및 경영진 무능력 비판. 19조 부채, 연속 하락 기록하며 투자 부적합 의견 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['디스플레이', '중국', '부채']</t>
+          <t>['중국 경쟁', '부채', '연속 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1743000</v>
+        <v>1744000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.91%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G15" t="n">
-        <v>1451</v>
+        <v>1488</v>
       </c>
       <c r="H15" t="n">
         <v>50.2</v>
@@ -1806,7 +1806,7 @@
         <v>50.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2391041164000</v>
+        <v>2441640119500</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>9월 악재 소멸 후 상승 기대감. JP모간의 매수세 유입 감지.</t>
+          <t>정치적 언급이 다수이며, 특정 시점 이후 악재 소멸 및 상승 기대감 표출. 외인, 기관 매도 요청.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['악재 소멸', '상승', '매수세']</t>
+          <t>['악재 소멸', '상승 기대', '외국인']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13790</v>
+        <v>13810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.29%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>13155731000</v>
+        <v>13396239050</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 변동성에 따른 등락 반복 및 단기 차익 거래 패턴 관찰.</t>
+          <t>유가 변동성 속에서 단기적인 등락 예상. 외국인 매수 및 매도 관측, VI 발동 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', '변동성', '차익거래']</t>
+          <t>['유가', '외국인', 'VI']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3435</v>
+        <v>13200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.85</v>
+        <v>1.36</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="H17" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3520</v>
+        <v>13530</v>
       </c>
       <c r="K17" t="n">
-        <v>3730</v>
+        <v>14280</v>
       </c>
       <c r="L17" t="n">
-        <v>3750</v>
+        <v>14800</v>
       </c>
       <c r="M17" t="n">
-        <v>3420</v>
+        <v>12960</v>
       </c>
       <c r="N17" t="n">
-        <v>3.11</v>
+        <v>0.4</v>
       </c>
       <c r="O17" t="n">
-        <v>5208273243</v>
+        <v>79433115170</v>
       </c>
       <c r="P17" t="n">
-        <v>16110</v>
+        <v>25700</v>
       </c>
       <c r="Q17" t="n">
-        <v>2300</v>
+        <v>4600</v>
       </c>
       <c r="R17" t="n">
-        <v>-279000</v>
+        <v>-64000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 및 급격한 주가 하락세. 투자자들의 차익 실현 및 부정적 심리 확산.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장폐지', '급락', '차익실현']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,82 +2023,82 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10170</v>
+        <v>3430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.8</v>
+        <v>-0.85</v>
       </c>
       <c r="E18" t="n">
+        <v>92</v>
+      </c>
+      <c r="F18" t="n">
         <v>50</v>
       </c>
-      <c r="F18" t="n">
-        <v>35</v>
-      </c>
       <c r="G18" t="n">
-        <v>114</v>
+        <v>289</v>
       </c>
       <c r="H18" t="n">
-        <v>18.42</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10460</v>
+        <v>3520</v>
       </c>
       <c r="K18" t="n">
-        <v>10860</v>
+        <v>3730</v>
       </c>
       <c r="L18" t="n">
-        <v>11150</v>
+        <v>3750</v>
       </c>
       <c r="M18" t="n">
-        <v>10060</v>
+        <v>3420</v>
       </c>
       <c r="N18" t="n">
-        <v>19.22</v>
+        <v>3.11</v>
       </c>
       <c r="O18" t="n">
-        <v>54338950265</v>
+        <v>5241297518</v>
       </c>
       <c r="P18" t="n">
-        <v>22450</v>
+        <v>16110</v>
       </c>
       <c r="Q18" t="n">
-        <v>1760</v>
+        <v>2300</v>
       </c>
       <c r="R18" t="n">
-        <v>-60000</v>
+        <v>-279000</v>
       </c>
       <c r="S18" t="n">
-        <v>-2000</v>
+        <v>-9000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>종목의 급락 및 상폐 가능성에 대한 부정적 언급이 주를 이루며, 차익 실현 의지와 보유 종목에 대한 불만을 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,90 +2107,90 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['상폐', '차익', '폭락']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13110</v>
+        <v>10190</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.10%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.36</v>
+        <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H19" t="n">
-        <v>1.76</v>
+        <v>18.42</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13530</v>
+        <v>10460</v>
       </c>
       <c r="K19" t="n">
-        <v>14280</v>
+        <v>10860</v>
       </c>
       <c r="L19" t="n">
-        <v>14800</v>
+        <v>11150</v>
       </c>
       <c r="M19" t="n">
-        <v>12960</v>
+        <v>10060</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4</v>
+        <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>79018378185</v>
+        <v>54518249430</v>
       </c>
       <c r="P19" t="n">
-        <v>25700</v>
+        <v>22450</v>
       </c>
       <c r="Q19" t="n">
-        <v>4600</v>
+        <v>1760</v>
       </c>
       <c r="R19" t="n">
-        <v>-64000</v>
+        <v>-60000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2234,13 @@
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>43984109072</v>
+        <v>44323777958</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_12.xlsx
+++ b/data/trending_integrated_20260917_12.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1707</v>
+        <v>75</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.19%</t>
+          <t>'+33.93%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="H2" t="n">
-        <v>3.52</v>
+        <v>3.71</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1397</v>
+        <v>56</v>
       </c>
       <c r="K2" t="n">
-        <v>1395</v>
+        <v>56</v>
       </c>
       <c r="L2" t="n">
-        <v>1800</v>
+        <v>90</v>
       </c>
       <c r="M2" t="n">
-        <v>1369</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="O2" t="n">
-        <v>44823405132</v>
+        <v>475181147</v>
       </c>
       <c r="P2" t="n">
-        <v>5140</v>
+        <v>901</v>
       </c>
       <c r="Q2" t="n">
-        <v>870</v>
+        <v>56</v>
       </c>
       <c r="R2" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
+          <t>주가 부양에 대한 의구심과 함께 희망고문, 지분 매수 공시 부재, 코다코 부채 언급. BPS 715원.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['우주', '스페이스X', '유상증자']</t>
+          <t>['희망고문', '지분 공시']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,43 +643,43 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>321370</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>21850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.43%</t>
+          <t>'+28.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="H3" t="n">
-        <v>3.71</v>
+        <v>2.61</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>56</v>
+        <v>16950</v>
       </c>
       <c r="K3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.71</v>
+        <v>1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>432471722</v>
+        <v>267384000000</v>
       </c>
       <c r="P3" t="n">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>마이크로LED, AI 데이터센터 관련 기대감 속에서 300원 이상 상승 희망. BPS 715원 언급.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['마이크로LED', 'AI 데이터센터', 'BPS']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4600</v>
+        <v>1700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.79%</t>
+          <t>'+21.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>447</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>202</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>1115</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
-        <v>0.95</v>
+        <v>3.52</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3840</v>
+        <v>1397</v>
       </c>
       <c r="K4" t="n">
-        <v>4170</v>
+        <v>1395</v>
       </c>
       <c r="L4" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="M4" t="n">
-        <v>3990</v>
+        <v>1369</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>222264989520</v>
+        <v>45497497869</v>
       </c>
       <c r="P4" t="n">
-        <v>6900</v>
+        <v>5140</v>
       </c>
       <c r="Q4" t="n">
-        <v>1738</v>
+        <v>870</v>
       </c>
       <c r="R4" t="n">
-        <v>-159000</v>
+        <v>72000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>카카오 또는 소프트뱅크의 인수 가능성 언급. 10배 상승 및 1만원 이상 시가총액 기대. 거래량 급증.</t>
+          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인수', '소프트뱅크', '텐버거']</t>
+          <t>['우주', '스페이스X', '유상증자']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>321370</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21850</v>
+        <v>4630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.73%</t>
+          <t>'+20.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="G5" t="n">
-        <v>236</v>
+        <v>1141</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>0.95</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18560</v>
+        <v>3840</v>
       </c>
       <c r="K5" t="n">
-        <v>19260</v>
+        <v>4170</v>
       </c>
       <c r="L5" t="n">
-        <v>22950</v>
+        <v>4800</v>
       </c>
       <c r="M5" t="n">
-        <v>18920</v>
+        <v>3990</v>
       </c>
       <c r="N5" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="O5" t="n">
-        <v>262141144870</v>
+        <v>225856919029</v>
       </c>
       <c r="P5" t="n">
-        <v>59600</v>
+        <v>6900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1030</v>
+        <v>1738</v>
       </c>
       <c r="R5" t="n">
-        <v>-78000</v>
+        <v>-159000</v>
       </c>
       <c r="S5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>자회사 ADS테크의 CPO 생산 장비 수주 및 삼성 공급 계약 발표. AI 인프라 사업 확장 기대감.</t>
+          <t>카카오 및 소프트뱅크 인수 가능성, 텐버거 기대감, 손바뀜 관찰. 높은 거래량과 인수가격 1만원 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['CPO', '수주', 'AI 인프라']</t>
+          <t>['인수', '텐버거']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3845</v>
+        <v>3830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.86%</t>
+          <t>'+9.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>85556855718</v>
+        <v>86603602260</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>스페이스X 관련 이슈로 인한 변동성 장세. 프로그램 매수와 매도세가 공존하며 방향성 부재.</t>
+          <t>프로그램 매수세 유입 및 스페이스X 관련 이슈로 인한 상승 기대감. 4,000원 돌파 및 5천원 돌파 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '프로그램매매', '변동성']</t>
+          <t>['스페이스X', '매집봉']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21600</v>
+        <v>21575</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.93%</t>
+          <t>'+6.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>57278867775</v>
+        <v>58541625800</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 금리 인상 영향 속에서 장기 보유 및 분할 매수 관점 제시. 스퀴즈온 기대.</t>
+          <t>나스닥 반등과 자사주 소각 공시 기대감 속에서 60일선 돌파 및 추세 전환 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['나스닥', '금리인상', '스퀴즈온']</t>
+          <t>['추세 전환', '자사주 소각']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10460</v>
+        <v>10360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.91%</t>
+          <t>'+3.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>169601165085</v>
+        <v>171531555435</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1228,7 +1228,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>49779661580</v>
+        <v>50339212060</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85600</v>
+        <v>85800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F10" t="n">
         <v>106</v>
       </c>
       <c r="G10" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>86196855300</v>
+        <v>87494354750</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253250</v>
+        <v>16280</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.10%</t>
+          <t>'+1.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>224</v>
       </c>
       <c r="F11" t="n">
-        <v>441</v>
+        <v>123</v>
       </c>
       <c r="G11" t="n">
-        <v>1761</v>
+        <v>1221</v>
       </c>
       <c r="H11" t="n">
-        <v>46.52</v>
+        <v>4.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>250500</v>
+        <v>16100</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>16750</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>15560</v>
       </c>
       <c r="N11" t="n">
-        <v>46.56</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>1349559000000</v>
+        <v>322546075335</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-199000</v>
+        <v>-508000</v>
       </c>
       <c r="S11" t="n">
-        <v>-55000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 논쟁이 주된 내용으로, 주가 및 실적 관련 구체적인 내용은 부재.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '대선', '주식방']</t>
+          <t>['광통신', '미국', '수혜']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16150</v>
+        <v>18620</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.31%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.93</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>219</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>1213</v>
+        <v>308</v>
       </c>
       <c r="H12" t="n">
-        <v>4.88</v>
+        <v>10.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16100</v>
+        <v>18570</v>
       </c>
       <c r="K12" t="n">
-        <v>16200</v>
+        <v>18740</v>
       </c>
       <c r="L12" t="n">
-        <v>16750</v>
+        <v>18900</v>
       </c>
       <c r="M12" t="n">
-        <v>15560</v>
+        <v>18510</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>315179767470</v>
+        <v>43238149995</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-508000</v>
+        <v>-175000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
+          <t>6천억 수주 발표에도 음봉 기록. 금리 인상 및 대차해지 운동 독려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '수혜']</t>
+          <t>['수주', '금리인상', '대차해지']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18590</v>
+        <v>254000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>443</v>
       </c>
       <c r="G13" t="n">
-        <v>305</v>
+        <v>1737</v>
       </c>
       <c r="H13" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18570</v>
+        <v>253500</v>
       </c>
       <c r="K13" t="n">
-        <v>18740</v>
+        <v>257000</v>
       </c>
       <c r="L13" t="n">
-        <v>18900</v>
+        <v>259000</v>
       </c>
       <c r="M13" t="n">
-        <v>18510</v>
+        <v>252000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64</v>
+        <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>42494992580</v>
+        <v>1410229443250</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>77100</v>
       </c>
       <c r="R13" t="n">
-        <v>-175000</v>
+        <v>-199000</v>
       </c>
       <c r="S13" t="n">
-        <v>-31000</v>
+        <v>-55000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6천억 수주 발표에도 음봉 기록. 금리 인상 및 대차해지 운동 독려.</t>
+          <t>게시글은 정치적 내용 위주로 구성되어 있으며, 주가 관련 내용은 미미함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '금리인상', '대차해지']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8400</v>
+        <v>1750000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.51%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>116</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>470</v>
       </c>
       <c r="G14" t="n">
-        <v>281</v>
+        <v>1509</v>
       </c>
       <c r="H14" t="n">
-        <v>26.54</v>
+        <v>50.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8470</v>
+        <v>1759000</v>
       </c>
       <c r="K14" t="n">
-        <v>8470</v>
+        <v>1770000</v>
       </c>
       <c r="L14" t="n">
-        <v>8510</v>
+        <v>1785000</v>
       </c>
       <c r="M14" t="n">
-        <v>8360</v>
+        <v>1735000</v>
       </c>
       <c r="N14" t="n">
-        <v>26.66</v>
+        <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>9408745110</v>
+        <v>2521759292500</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>-263000</v>
+        <v>-161000</v>
       </c>
       <c r="S14" t="n">
-        <v>4000</v>
+        <v>-55000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중국 경쟁 심화 및 경영진 무능력 비판. 19조 부채, 연속 하락 기록하며 투자 부적합 의견 다수.</t>
+          <t>1년 전 관점 유지 및 9월 악재 소멸 후 상승 기대감 있으나, 일부 악재 및 외국인/기관 매도 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['중국 경쟁', '부채', '연속 하락']</t>
+          <t>['악재 소멸', '상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1744000</v>
+        <v>8390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.85%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>116</v>
       </c>
       <c r="F15" t="n">
-        <v>474</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>1488</v>
+        <v>317</v>
       </c>
       <c r="H15" t="n">
-        <v>50.2</v>
+        <v>26.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1759000</v>
+        <v>8470</v>
       </c>
       <c r="K15" t="n">
-        <v>1770000</v>
+        <v>8470</v>
       </c>
       <c r="L15" t="n">
-        <v>1785000</v>
+        <v>8510</v>
       </c>
       <c r="M15" t="n">
-        <v>1735000</v>
+        <v>8360</v>
       </c>
       <c r="N15" t="n">
-        <v>50.2</v>
+        <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>2441640119500</v>
+        <v>9972138945</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-161000</v>
+        <v>-263000</v>
       </c>
       <c r="S15" t="n">
-        <v>-55000</v>
+        <v>4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 언급이 다수이며, 특정 시점 이후 악재 소멸 및 상승 기대감 표출. 외인, 기관 매도 요청.</t>
+          <t>부정적인 전망과 함께 높은 부채 비율, 목표가 하향, 5일 연속 하락 등 악재 언급. 일부 추가 매수 의견도 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['악재 소멸', '상승 기대', '외국인']</t>
+          <t>['부채 비율', '목표가 하향']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13810</v>
+        <v>13750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-1.57%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G16" t="n">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>13396239050</v>
+        <v>13597819740</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 변동성 속에서 단기적인 등락 예상. 외국인 매수 및 매도 관측, VI 발동 가능성 언급.</t>
+          <t>유가 관련 변동성 언급, 외국인 대량 매수 및 매도 패턴 관찰. VI 예상 및 400~300원 띠기 가능성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', '외국인', 'VI']</t>
+          <t>['유가', 'VI']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13200</v>
+        <v>3455</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-1.85%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.36</v>
+        <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="H17" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13530</v>
+        <v>3520</v>
       </c>
       <c r="K17" t="n">
-        <v>14280</v>
+        <v>3730</v>
       </c>
       <c r="L17" t="n">
-        <v>14800</v>
+        <v>3750</v>
       </c>
       <c r="M17" t="n">
-        <v>12960</v>
+        <v>3420</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4</v>
+        <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>79433115170</v>
+        <v>5283546798</v>
       </c>
       <c r="P17" t="n">
-        <v>25700</v>
+        <v>16110</v>
       </c>
       <c r="Q17" t="n">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="R17" t="n">
-        <v>-64000</v>
+        <v>-279000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>주가 하락 및 상폐 가능성 언급, 부정적인 전망과 함께 차익 실현 및 매도 의견 다수.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,43 +2023,43 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3430</v>
+        <v>13250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.56%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.85</v>
+        <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3520</v>
+        <v>13530</v>
       </c>
       <c r="K18" t="n">
-        <v>3730</v>
+        <v>14280</v>
       </c>
       <c r="L18" t="n">
-        <v>3750</v>
+        <v>14800</v>
       </c>
       <c r="M18" t="n">
-        <v>3420</v>
+        <v>12960</v>
       </c>
       <c r="N18" t="n">
-        <v>3.11</v>
+        <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>5241297518</v>
+        <v>80280442520</v>
       </c>
       <c r="P18" t="n">
-        <v>16110</v>
+        <v>25700</v>
       </c>
       <c r="Q18" t="n">
-        <v>2300</v>
+        <v>4600</v>
       </c>
       <c r="R18" t="n">
-        <v>-279000</v>
+        <v>-64000</v>
       </c>
       <c r="S18" t="n">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>종목의 급락 및 상폐 가능성에 대한 부정적 언급이 주를 이루며, 차익 실현 의지와 보유 종목에 대한 불만을 표출.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['상폐', '차익', '폭락']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10190</v>
+        <v>10230</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.58%</t>
+          <t>'-2.20%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>54518249430</v>
+        <v>54976686360</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4085</v>
+        <v>4135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.37%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G20" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>44323777958</v>
+        <v>45096061007</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_12.xlsx
+++ b/data/trending_integrated_20260917_12.xlsx
@@ -584,7 +584,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주가 부양에 대한 의구심과 함께 희망고문, 지분 매수 공시 부재, 코다코 부채 언급. BPS 715원.</t>
+          <t>급등 후 횡보 구간에서 개인 매수세 유입 및 300원 돌파 기대감. BPS 대비 저평가 가능성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['희망고문', '지분 공시']</t>
+          <t>['상승', '개미', 'BPS']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21850</v>
+        <v>4645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.91%</t>
+          <t>'+20.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>472</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="G3" t="n">
-        <v>233</v>
+        <v>1161</v>
       </c>
       <c r="H3" t="n">
-        <v>2.61</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16950</v>
+        <v>3840</v>
       </c>
       <c r="K3" t="n">
+        <v>4170</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4800</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3990</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O3" t="n">
+        <v>230647487705</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6900</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-159000</v>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O3" t="n">
-        <v>267384000000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-78000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3000</v>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
+          <t>카카오 및 소프트뱅크 인수 가능성, 텐버거 기대감, 손바뀜 관찰. 높은 거래량과 인수가격 1만원 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CPO', '수주 공시']</t>
+          <t>['인수', '텐버거']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1700</v>
+        <v>1683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.69%</t>
+          <t>'+20.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H4" t="n">
         <v>3.52</v>
@@ -794,7 +794,7 @@
         <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>45497497869</v>
+        <v>45876773829</v>
       </c>
       <c r="P4" t="n">
         <v>5140</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4630</v>
+        <v>21800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+20.57%</t>
+          <t>'+17.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>1141</v>
+        <v>251</v>
       </c>
       <c r="H5" t="n">
-        <v>0.95</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3840</v>
+        <v>18560</v>
       </c>
       <c r="K5" t="n">
-        <v>4170</v>
+        <v>19260</v>
       </c>
       <c r="L5" t="n">
-        <v>4800</v>
+        <v>22950</v>
       </c>
       <c r="M5" t="n">
-        <v>3990</v>
+        <v>18920</v>
       </c>
       <c r="N5" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>225856919029</v>
+        <v>269145773870</v>
       </c>
       <c r="P5" t="n">
-        <v>6900</v>
+        <v>59600</v>
       </c>
       <c r="Q5" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R5" t="n">
-        <v>-159000</v>
+        <v>-78000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>카카오 및 소프트뱅크 인수 가능성, 텐버거 기대감, 손바뀜 관찰. 높은 거래량과 인수가격 1만원 언급.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['인수', '텐버거']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3830</v>
+        <v>3825</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.43%</t>
+          <t>'+9.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
         <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>86603602260</v>
+        <v>87197994822</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21575</v>
+        <v>21700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.81%</t>
+          <t>'+7.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>58541625800</v>
+        <v>61826512475</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등과 자사주 소각 공시 기대감 속에서 60일선 돌파 및 추세 전환 가능성 언급.</t>
+          <t>나스닥 반등 및 FDC 수주 기대감으로 인한 상승세 관측. 주포 교체 및 자사주 소각 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['추세 전환', '자사주 소각']</t>
+          <t>['수주', '금리', '주포']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10360</v>
+        <v>10430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>171531555435</v>
+        <v>172149029330</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료 관련 기대감 속에서 외국인 매도세 관측. 1조원 이상 예상 매출 언급.</t>
+          <t>낙태약 및 탈모치료 관련 기대감 속 매수세 유입. 외국인 및 차명계좌 매도세 관측.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모 치료', '매출 예상']</t>
+          <t>['낙태약', '탈모치료', '매출']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13350</v>
+        <v>13450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.33%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>50339212060</v>
+        <v>50639455240</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85800</v>
+        <v>86100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.74%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F10" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G10" t="n">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>87494354750</v>
+        <v>90442486100</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16280</v>
+        <v>16200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.12%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F11" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G11" t="n">
-        <v>1221</v>
+        <v>1234</v>
       </c>
       <c r="H11" t="n">
         <v>4.88</v>
@@ -1438,7 +1438,7 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>322546075335</v>
+        <v>325494029790</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18620</v>
+        <v>254250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>442</v>
       </c>
       <c r="G12" t="n">
-        <v>308</v>
+        <v>1773</v>
       </c>
       <c r="H12" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18570</v>
+        <v>253500</v>
       </c>
       <c r="K12" t="n">
-        <v>18740</v>
+        <v>257000</v>
       </c>
       <c r="L12" t="n">
-        <v>18900</v>
+        <v>259000</v>
       </c>
       <c r="M12" t="n">
-        <v>18510</v>
+        <v>252000</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>43238149995</v>
+        <v>1448145395750</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>77100</v>
       </c>
       <c r="R12" t="n">
-        <v>-175000</v>
+        <v>-199000</v>
       </c>
       <c r="S12" t="n">
-        <v>-31000</v>
+        <v>-55000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>6천억 수주 발표에도 음봉 기록. 금리 인상 및 대차해지 운동 독려.</t>
+          <t>정치적 논쟁이 주를 이루며, 특정 정치인에 대한 지지 및 비판이 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수주', '금리인상', '대차해지']</t>
+          <t>['정치', '지지율', '연기금']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>254000</v>
+        <v>18610</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>443</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>1737</v>
+        <v>317</v>
       </c>
       <c r="H13" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>253500</v>
+        <v>18570</v>
       </c>
       <c r="K13" t="n">
-        <v>257000</v>
+        <v>18740</v>
       </c>
       <c r="L13" t="n">
-        <v>259000</v>
+        <v>18900</v>
       </c>
       <c r="M13" t="n">
-        <v>252000</v>
+        <v>18510</v>
       </c>
       <c r="N13" t="n">
-        <v>46.56</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1410229443250</v>
+        <v>44056660725</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-199000</v>
+        <v>-175000</v>
       </c>
       <c r="S13" t="n">
-        <v>-55000</v>
+        <v>-31000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>게시글은 정치적 내용 위주로 구성되어 있으며, 주가 관련 내용은 미미함.</t>
+          <t>6천억 수주 발표에도 불구하고 음봉 마감. 대차해지 운동 동참 호소.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['수주', '대차해지', '금리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1750000</v>
+        <v>1754000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.51%</t>
+          <t>'-0.28%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="G14" t="n">
-        <v>1509</v>
+        <v>1537</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2521759292500</v>
+        <v>2577392951500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1년 전 관점 유지 및 9월 악재 소멸 후 상승 기대감 있으나, 일부 악재 및 외국인/기관 매도 관찰.</t>
+          <t>정치적 이슈 및 특정 인물 언급이 주를 이루며, 개별적인 주가 전망은 불분명.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['악재 소멸', '상승']</t>
+          <t>['정치', '악재', '자사주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8390</v>
+        <v>8400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>9972138945</v>
+        <v>10158156035</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13750</v>
+        <v>13760</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.57%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F16" t="n">
         <v>69</v>
       </c>
       <c r="G16" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>13597819740</v>
+        <v>13820386070</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3455</v>
+        <v>3445</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.85%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.85</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
         <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H17" t="n">
         <v>2.26</v>
@@ -1990,7 +1990,7 @@
         <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>5283546798</v>
+        <v>5309308796</v>
       </c>
       <c r="P17" t="n">
         <v>16110</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13250</v>
+        <v>13200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2082,7 +2082,7 @@
         <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>80280442520</v>
+        <v>80422855580</v>
       </c>
       <c r="P18" t="n">
         <v>25700</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10230</v>
+        <v>10180</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.20%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>54976686360</v>
+        <v>55166068055</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2234,13 +2234,13 @@
         <v>0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>45096061007</v>
+        <v>45454477681</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>

--- a/data/trending_integrated_20260917_12.xlsx
+++ b/data/trending_integrated_20260917_12.xlsx
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F2" t="n">
         <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H2" t="n">
         <v>3.71</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4645</v>
+        <v>4650</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.96%</t>
+          <t>'+21.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F3" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G3" t="n">
-        <v>1161</v>
+        <v>1181</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>230647487705</v>
+        <v>233121994948</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오 및 소프트뱅크 인수 가능성, 텐버거 기대감, 손바뀜 관찰. 높은 거래량과 인수가격 1만원 언급.</t>
+          <t>소프트뱅크의 통큰 인수 가능성 및 카카오와의 협력에 따른 텐버거 기대감. 높은 거래량 및 손바뀜 관측.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수', '텐버거']</t>
+          <t>['소프트뱅크 인수', '텐버거', '손바뀜']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.47%</t>
+          <t>'+20.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H4" t="n">
         <v>3.52</v>
@@ -794,7 +794,7 @@
         <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>45876773829</v>
+        <v>46166120179</v>
       </c>
       <c r="P4" t="n">
         <v>5140</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21800</v>
+        <v>21850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.46%</t>
+          <t>'+17.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>269145773870</v>
+        <v>270789430645</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3825</v>
+        <v>3855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.29%</t>
+          <t>'+10.14%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>87197994822</v>
+        <v>87910484926</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>프로그램 매수세 유입 및 스페이스X 관련 이슈로 인한 상승 기대감. 4,000원 돌파 및 5천원 돌파 전망.</t>
+          <t>스페이스X 관련주로 부각되며 4,000원 돌파 및 5,000원 돌파 기대감. 일부 투자자들의 매집봉 관측 및 매도 의견 공존.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['스페이스X', '매집봉']</t>
+          <t>['스페이스X', '매집봉', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1061,7 +1061,7 @@
         <v>20450</v>
       </c>
       <c r="L7" t="n">
-        <v>21750</v>
+        <v>21800</v>
       </c>
       <c r="M7" t="n">
         <v>20450</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>61826512475</v>
+        <v>65541222350</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>나스닥 반등 및 FDC 수주 기대감으로 인한 상승세 관측. 주포 교체 및 자사주 소각 가능성 언급.</t>
+          <t>금리 인상 속에서도 60일선 돌파 및 추세 전환 기대감. 내일 FDC 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '금리', '주포']</t>
+          <t>['60일선', '추세 전환', 'FDC 수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G8" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>172149029330</v>
+        <v>172504527125</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13450</v>
+        <v>13410</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.10%</t>
+          <t>'+3.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>50639455240</v>
+        <v>51493372215</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86100</v>
+        <v>86200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.74%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G10" t="n">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>90442486100</v>
+        <v>91322037100</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16200</v>
+        <v>16270</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>1234</v>
+        <v>1250</v>
       </c>
       <c r="H11" t="n">
         <v>4.88</v>
@@ -1438,7 +1438,7 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>325494029790</v>
+        <v>328077617320</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 수혜 기대감. 2연상 및 2만원 돌파 전망.</t>
+          <t>미국 광통신주 급등에 따른 국내 광통신주 동반 상승 기대. 2만 원 목표 및 통신 장비 부족 호재 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '미국', '수혜']</t>
+          <t>['광통신', '통신 장비', '매물대 소화']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>254250</v>
+        <v>18670</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
-        <v>442</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>1773</v>
+        <v>328</v>
       </c>
       <c r="H12" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>253500</v>
+        <v>18570</v>
       </c>
       <c r="K12" t="n">
-        <v>257000</v>
+        <v>18740</v>
       </c>
       <c r="L12" t="n">
-        <v>259000</v>
+        <v>18900</v>
       </c>
       <c r="M12" t="n">
-        <v>252000</v>
+        <v>18510</v>
       </c>
       <c r="N12" t="n">
-        <v>46.56</v>
+        <v>10.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1448145395750</v>
+        <v>44864718020</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>77100</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-199000</v>
+        <v>-175000</v>
       </c>
       <c r="S12" t="n">
-        <v>-55000</v>
+        <v>-31000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 논쟁이 주를 이루며, 특정 정치인에 대한 지지 및 비판이 혼재.</t>
+          <t>6천억 수주 발표에도 불구하고 음봉 마감. 대차해지 운동 동참 호소.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '지지율', '연기금']</t>
+          <t>['수주', '대차해지', '금리']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18610</v>
+        <v>254000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>445</v>
       </c>
       <c r="G13" t="n">
-        <v>317</v>
+        <v>1764</v>
       </c>
       <c r="H13" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18570</v>
+        <v>253500</v>
       </c>
       <c r="K13" t="n">
-        <v>18740</v>
+        <v>257000</v>
       </c>
       <c r="L13" t="n">
-        <v>18900</v>
+        <v>259000</v>
       </c>
       <c r="M13" t="n">
-        <v>18510</v>
+        <v>252000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64</v>
+        <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>44056660725</v>
+        <v>1489622433250</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>77100</v>
       </c>
       <c r="R13" t="n">
-        <v>-175000</v>
+        <v>-199000</v>
       </c>
       <c r="S13" t="n">
-        <v>-31000</v>
+        <v>-55000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6천억 수주 발표에도 불구하고 음봉 마감. 대차해지 운동 동참 호소.</t>
+          <t>정치적 논쟁으로 인해 주식 관련 내용 부재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '대차해지', '금리']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1754000</v>
+        <v>1752000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.28%</t>
+          <t>'-0.40%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G14" t="n">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2577392951500</v>
+        <v>2652079661500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 특정 인물 언급이 주를 이루며, 개별적인 주가 전망은 불분명.</t>
+          <t>하락장 속에서도 개인 투자자들의 홀딩 및 일부 매수 관점 존재. 자사주 매입 지연에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['정치', '악재', '자사주']</t>
+          <t>['홀딩', '자사주 매입', '개인 투자']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8400</v>
+        <v>8410</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.71%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F15" t="n">
         <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H15" t="n">
         <v>26.54</v>
@@ -1806,7 +1806,7 @@
         <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>10158156035</v>
+        <v>10273730485</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13760</v>
+        <v>13730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>13820386070</v>
+        <v>14022987955</v>
       </c>
       <c r="P16" t="n">
         <v>36200</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3445</v>
+        <v>3450</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.13%</t>
+          <t>'-1.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,7 +1961,7 @@
         <v>97</v>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
         <v>294</v>
@@ -1990,7 +1990,7 @@
         <v>3.11</v>
       </c>
       <c r="O17" t="n">
-        <v>5309308796</v>
+        <v>5325992576</v>
       </c>
       <c r="P17" t="n">
         <v>16110</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 하락 및 상폐 가능성 언급, 부정적인 전망과 함께 차익 실현 및 매도 의견 다수.</t>
+          <t>급락 및 상장폐지 가능성에 대한 우려 제기. 사기 주식 및 폭락에 대한 경고와 금감원 조사 촉구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['상장폐지', '폭락', '사기 주식']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,70 +2035,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>빛샘전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13200</v>
+        <v>10240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-2.10%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.36</v>
+        <v>-0.8</v>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>18.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13530</v>
+        <v>10460</v>
       </c>
       <c r="K18" t="n">
-        <v>14280</v>
+        <v>10860</v>
       </c>
       <c r="L18" t="n">
-        <v>14800</v>
+        <v>11150</v>
       </c>
       <c r="M18" t="n">
-        <v>12960</v>
+        <v>10060</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4</v>
+        <v>19.22</v>
       </c>
       <c r="O18" t="n">
-        <v>80422855580</v>
+        <v>55530604570</v>
       </c>
       <c r="P18" t="n">
-        <v>25700</v>
+        <v>22450</v>
       </c>
       <c r="Q18" t="n">
-        <v>4600</v>
+        <v>1760</v>
       </c>
       <c r="R18" t="n">
-        <v>-64000</v>
+        <v>-60000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '공급계약', '투자심리']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>072950</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>빛샘전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10180</v>
+        <v>13180</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.8</v>
+        <v>1.36</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="H19" t="n">
-        <v>18.42</v>
+        <v>1.76</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10460</v>
+        <v>13530</v>
       </c>
       <c r="K19" t="n">
-        <v>10860</v>
+        <v>14280</v>
       </c>
       <c r="L19" t="n">
-        <v>11150</v>
+        <v>14800</v>
       </c>
       <c r="M19" t="n">
-        <v>10060</v>
+        <v>12960</v>
       </c>
       <c r="N19" t="n">
-        <v>19.22</v>
+        <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>55166068055</v>
+        <v>80643609495</v>
       </c>
       <c r="P19" t="n">
-        <v>22450</v>
+        <v>25700</v>
       </c>
       <c r="Q19" t="n">
-        <v>1760</v>
+        <v>4600</v>
       </c>
       <c r="R19" t="n">
-        <v>-60000</v>
+        <v>-64000</v>
       </c>
       <c r="S19" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>미국 광통신주 급등에 따른 기대감, 루멘텀 등 관련주 상승. 삼성 공급 계약 공시 확인.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['광통신', '공급계약', '투자심리']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>072950</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4135</v>
+        <v>4185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.24%</t>
+          <t>'-5.10%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
         <v>0.87</v>
@@ -2266,7 +2266,7 @@
         <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>45454477681</v>
+        <v>46215534443</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
